--- a/data/out/variants/v10_date_range_no_solar/summary_v10_date_range_no_solar.xlsx
+++ b/data/out/variants/v10_date_range_no_solar/summary_v10_date_range_no_solar.xlsx
@@ -523,19 +523,19 @@
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>-2.114961054670579</v>
+        <v>-2.114961054671577</v>
       </c>
       <c r="F2" t="n">
-        <v>142.0243161639689</v>
+        <v>142.0243161639947</v>
       </c>
       <c r="G2" t="n">
-        <v>30168.85123596487</v>
+        <v>30168.85123597453</v>
       </c>
       <c r="H2" t="n">
-        <v>173.6918283511486</v>
+        <v>173.6918283511764</v>
       </c>
       <c r="I2" t="n">
-        <v>109.5059893009329</v>
+        <v>109.5059893009629</v>
       </c>
       <c r="J2" t="n">
         <v>13105</v>
@@ -547,7 +547,7 @@
         <v>2621</v>
       </c>
       <c r="M2" t="n">
-        <v>0.03016042709350586</v>
+        <v>0.0365288257598877</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -574,19 +574,19 @@
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>-2.091262336429067</v>
+        <v>-2.091348608178908</v>
       </c>
       <c r="F3" t="n">
-        <v>141.4123786449781</v>
+        <v>141.414454588782</v>
       </c>
       <c r="G3" t="n">
-        <v>29939.32570015144</v>
+        <v>29940.16125460658</v>
       </c>
       <c r="H3" t="n">
-        <v>173.0298404904525</v>
+        <v>173.0322549544061</v>
       </c>
       <c r="I3" t="n">
-        <v>109.0025329000344</v>
+        <v>109.004601174236</v>
       </c>
       <c r="J3" t="n">
         <v>13105</v>
@@ -598,7 +598,7 @@
         <v>2621</v>
       </c>
       <c r="M3" t="n">
-        <v>0.02822566032409668</v>
+        <v>0.05066752433776855</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -625,19 +625,19 @@
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>-1.751532065405427</v>
+        <v>-1.75784604070178</v>
       </c>
       <c r="F4" t="n">
-        <v>131.9393451754832</v>
+        <v>132.1071288940785</v>
       </c>
       <c r="G4" t="n">
-        <v>26648.98857330408</v>
+        <v>26710.14034312721</v>
       </c>
       <c r="H4" t="n">
-        <v>163.2451793263865</v>
+        <v>163.4323723841981</v>
       </c>
       <c r="I4" t="n">
-        <v>102.5505010165946</v>
+        <v>102.7131618733438</v>
       </c>
       <c r="J4" t="n">
         <v>13105</v>
@@ -649,7 +649,7 @@
         <v>2621</v>
       </c>
       <c r="M4" t="n">
-        <v>3.814326524734497</v>
+        <v>3.693885087966919</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -680,19 +680,19 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>-11.80645678979062</v>
+        <v>-11.79418733112211</v>
       </c>
       <c r="F5" t="n">
-        <v>337.8572936738765</v>
+        <v>337.7108998026409</v>
       </c>
       <c r="G5" t="n">
-        <v>124032.3981488315</v>
+        <v>123913.5666556541</v>
       </c>
       <c r="H5" t="n">
-        <v>352.1823365088482</v>
+        <v>352.0135887372164</v>
       </c>
       <c r="I5" t="n">
-        <v>286.1087880876762</v>
+        <v>285.9393166500828</v>
       </c>
       <c r="J5" t="n">
         <v>13105</v>
@@ -704,7 +704,7 @@
         <v>2621</v>
       </c>
       <c r="M5" t="n">
-        <v>3.364603996276855</v>
+        <v>2.836915731430054</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>-497.6684110193031</v>
+        <v>-497.5113174664902</v>
       </c>
     </row>
     <row r="6">
@@ -733,23 +733,23 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>{'max_depth': 5, 'min_samples_split': 2}</t>
+          <t>{'max_depth': None, 'min_samples_split': 5}</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>-0.8594765416793877</v>
+        <v>-3.110557026960132</v>
       </c>
       <c r="F6" t="n">
-        <v>100.6316982955585</v>
+        <v>121.0727797914282</v>
       </c>
       <c r="G6" t="n">
-        <v>18009.30097619616</v>
+        <v>39811.34314901569</v>
       </c>
       <c r="H6" t="n">
-        <v>134.1987368651291</v>
+        <v>199.5278004414816</v>
       </c>
       <c r="I6" t="n">
-        <v>80.80078396323029</v>
+        <v>97.66683045366771</v>
       </c>
       <c r="J6" t="n">
         <v>13105</v>
@@ -761,7 +761,7 @@
         <v>2621</v>
       </c>
       <c r="M6" t="n">
-        <v>0.9852924346923828</v>
+        <v>1.107896089553833</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>-508.2349105009467</v>
+        <v>-518.940568992421</v>
       </c>
     </row>
     <row r="7">
@@ -794,19 +794,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>-1.286765595352681</v>
+        <v>-1.289229774706457</v>
       </c>
       <c r="F7" t="n">
-        <v>127.6722492864515</v>
+        <v>127.7205102042927</v>
       </c>
       <c r="G7" t="n">
-        <v>22147.65765827964</v>
+        <v>22171.52359401304</v>
       </c>
       <c r="H7" t="n">
-        <v>148.8208912024103</v>
+        <v>148.9010530319146</v>
       </c>
       <c r="I7" t="n">
-        <v>104.8812952692433</v>
+        <v>104.917730302434</v>
       </c>
       <c r="J7" t="n">
         <v>13105</v>
@@ -818,7 +818,7 @@
         <v>2621</v>
       </c>
       <c r="M7" t="n">
-        <v>283.8427536487579</v>
+        <v>266.3381454944611</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="O7" t="n">
-        <v>-501.1642679444355</v>
+        <v>-499.4331232774675</v>
       </c>
     </row>
     <row r="8">
@@ -851,19 +851,19 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>-6.576640508362147</v>
+        <v>-6.583313884403164</v>
       </c>
       <c r="F8" t="n">
-        <v>261.2220719078157</v>
+        <v>261.3569560539044</v>
       </c>
       <c r="G8" t="n">
-        <v>73380.86619812845</v>
+        <v>73445.49881647892</v>
       </c>
       <c r="H8" t="n">
-        <v>270.8890293055968</v>
+        <v>271.008300272296</v>
       </c>
       <c r="I8" t="n">
-        <v>220.6565655970103</v>
+        <v>220.7807335878979</v>
       </c>
       <c r="J8" t="n">
         <v>13105</v>
@@ -875,7 +875,7 @@
         <v>2621</v>
       </c>
       <c r="M8" t="n">
-        <v>178.9411287307739</v>
+        <v>147.6265518665314</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="O8" t="n">
-        <v>-454.1189229255622</v>
+        <v>-454.1219567644232</v>
       </c>
     </row>
     <row r="9">
@@ -908,19 +908,19 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>-18.45730759289028</v>
+        <v>-18.45820714073911</v>
       </c>
       <c r="F9" t="n">
-        <v>427.6706320855166</v>
+        <v>427.6808734612775</v>
       </c>
       <c r="G9" t="n">
-        <v>188446.8562912402</v>
+        <v>188455.5685430965</v>
       </c>
       <c r="H9" t="n">
-        <v>434.104660526975</v>
+        <v>434.1146951476032</v>
       </c>
       <c r="I9" t="n">
-        <v>357.7806706006843</v>
+        <v>357.7889149133475</v>
       </c>
       <c r="J9" t="n">
         <v>13105</v>
@@ -932,7 +932,7 @@
         <v>2621</v>
       </c>
       <c r="M9" t="n">
-        <v>23.47905969619751</v>
+        <v>21.7180860042572</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="O9" t="n">
-        <v>-482.782787755956</v>
+        <v>-482.7835890548506</v>
       </c>
     </row>
     <row r="10">
@@ -965,19 +965,19 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>-2.269710331220058</v>
+        <v>-2.348029511362685</v>
       </c>
       <c r="F10" t="n">
-        <v>141.0556063661634</v>
+        <v>143.3609249468578</v>
       </c>
       <c r="G10" t="n">
-        <v>31667.62050503624</v>
+        <v>32426.15316505228</v>
       </c>
       <c r="H10" t="n">
-        <v>177.953984234791</v>
+        <v>180.0726330263771</v>
       </c>
       <c r="I10" t="n">
-        <v>117.6436389749101</v>
+        <v>119.3874992325078</v>
       </c>
       <c r="J10" t="n">
         <v>13105</v>
@@ -989,7 +989,7 @@
         <v>2621</v>
       </c>
       <c r="M10" t="n">
-        <v>0.5216078758239746</v>
+        <v>0.5703930854797363</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         </is>
       </c>
       <c r="O10" t="n">
-        <v>-572.8621279508374</v>
+        <v>-570.491871472152</v>
       </c>
     </row>
     <row r="11">
@@ -1018,23 +1018,23 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>{'n_estimators': 246, 'learning_rate': 0.010974706495725335, 'max_depth': 7, 'subsample': 0.8254851017526658, 'colsample_bytree': 0.8538691522691684}</t>
+          <t>{'n_estimators': 276, 'learning_rate': 0.010302993225070176, 'max_depth': 6, 'subsample': 0.8769391770311147, 'colsample_bytree': 0.9986808236625948}</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>-2.387434376410749</v>
+        <v>-2.246024028676503</v>
       </c>
       <c r="F11" t="n">
-        <v>158.6013697309032</v>
+        <v>155.2886522540952</v>
       </c>
       <c r="G11" t="n">
-        <v>32807.79501891297</v>
+        <v>31438.21521706479</v>
       </c>
       <c r="H11" t="n">
-        <v>181.129221880162</v>
+        <v>177.3082491512022</v>
       </c>
       <c r="I11" t="n">
-        <v>133.2611526754682</v>
+        <v>130.1446294818517</v>
       </c>
       <c r="J11" t="n">
         <v>13105</v>
@@ -1046,7 +1046,7 @@
         <v>2621</v>
       </c>
       <c r="M11" t="n">
-        <v>140.4806926250458</v>
+        <v>74.73625183105469</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1073,23 +1073,23 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>{'n_estimators': 343, 'learning_rate': 0.018249882020099008, 'num_leaves': 31, 'min_child_samples': 10}</t>
+          <t>{'n_estimators': 251, 'learning_rate': 0.018474175005009776, 'num_leaves': 35, 'min_child_samples': 41}</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>-2.399446131613945</v>
+        <v>-1.860734331487225</v>
       </c>
       <c r="F12" t="n">
-        <v>153.8639910858233</v>
+        <v>136.9864277880147</v>
       </c>
       <c r="G12" t="n">
-        <v>32924.1306165169</v>
+        <v>27706.62841605981</v>
       </c>
       <c r="H12" t="n">
-        <v>181.4500774772965</v>
+        <v>166.453081725932</v>
       </c>
       <c r="I12" t="n">
-        <v>130.0263034329386</v>
+        <v>114.5180409003591</v>
       </c>
       <c r="J12" t="n">
         <v>13105</v>
@@ -1101,7 +1101,7 @@
         <v>2621</v>
       </c>
       <c r="M12" t="n">
-        <v>269.6337316036224</v>
+        <v>222.1546428203583</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1128,23 +1128,23 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>{'iterations': 458, 'learning_rate': 0.013190142798390956, 'depth': 8}</t>
+          <t>{'iterations': 443, 'learning_rate': 0.013976167882149143, 'depth': 8}</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>-3.018235619926823</v>
+        <v>-3.13028787402624</v>
       </c>
       <c r="F13" t="n">
-        <v>173.6778734879884</v>
+        <v>177.833845937801</v>
       </c>
       <c r="G13" t="n">
-        <v>38917.19688336443</v>
+        <v>40002.43927492213</v>
       </c>
       <c r="H13" t="n">
-        <v>197.2744202459215</v>
+        <v>200.0060980943384</v>
       </c>
       <c r="I13" t="n">
-        <v>146.0331061791274</v>
+        <v>149.674628703273</v>
       </c>
       <c r="J13" t="n">
         <v>13105</v>
@@ -1156,7 +1156,7 @@
         <v>2621</v>
       </c>
       <c r="M13" t="n">
-        <v>345.9620983600616</v>
+        <v>247.6639468669891</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1183,23 +1183,23 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>{'max_depth': 20, 'min_samples_split': 2, 'n_estimators': 100}</t>
+          <t>{'max_depth': 10, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>-1.902464210748014</v>
+        <v>-1.539931926457111</v>
       </c>
       <c r="F14" t="n">
-        <v>142.4860040298531</v>
+        <v>134.0864244180563</v>
       </c>
       <c r="G14" t="n">
-        <v>28110.78837100559</v>
+        <v>24599.61042654701</v>
       </c>
       <c r="H14" t="n">
-        <v>167.6627220672669</v>
+        <v>156.8426294938561</v>
       </c>
       <c r="I14" t="n">
-        <v>120.2227711153989</v>
+        <v>112.7351095201831</v>
       </c>
       <c r="J14" t="n">
         <v>13105</v>
@@ -1211,7 +1211,7 @@
         <v>2621</v>
       </c>
       <c r="M14" t="n">
-        <v>67.93722414970398</v>
+        <v>58.37687087059021</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         </is>
       </c>
       <c r="O14" t="n">
-        <v>-547.3967724996756</v>
+        <v>-557.807520821813</v>
       </c>
     </row>
     <row r="15">
@@ -1268,7 +1268,7 @@
         <v>2621</v>
       </c>
       <c r="M15" t="n">
-        <v>25.97622799873352</v>
+        <v>20.68915367126465</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -1301,19 +1301,19 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>-2.613337795077152</v>
+        <v>-2.6600837519467</v>
       </c>
       <c r="F16" t="n">
-        <v>156.0579480676188</v>
+        <v>156.9827587375639</v>
       </c>
       <c r="G16" t="n">
-        <v>34995.7025117607</v>
+        <v>35448.44390850004</v>
       </c>
       <c r="H16" t="n">
-        <v>187.0713834656725</v>
+        <v>188.2775714430692</v>
       </c>
       <c r="I16" t="n">
-        <v>122.8582490582419</v>
+        <v>123.7963216329578</v>
       </c>
       <c r="J16" t="n">
         <v>13105</v>
@@ -1325,7 +1325,7 @@
         <v>2621</v>
       </c>
       <c r="M16" t="n">
-        <v>518.8933064937592</v>
+        <v>455.2565472126007</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         </is>
       </c>
       <c r="O16" t="n">
-        <v>-514.9354020755803</v>
+        <v>-516.4337845230569</v>
       </c>
     </row>
   </sheetData>
